--- a/TESTS/zlit_6_stivenson.xlsx
+++ b/TESTS/zlit_6_stivenson.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Роберт Луїс Стівенсон — шотландський письменник майстер пригодницького жанру</t>
+          <t>Роберт Луїс Стівенсон</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Шотландія — Стівенсон народився в Единбурзі і є класиком шотландської та світової літератури</t>
+          <t>Шотландія</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Від Джима Хокінса — підлітка що став учасником пошуку піратського скарбу</t>
+          <t>Від Джима Хокінса</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Одноногий кок і колишній пірат — харизматичний лиходій що поєднує чарівність і підступність</t>
+          <t>Одноногий кок і колишній пірат</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Він неоднозначний — розумний харизматичний здатен на відданість але не зупиниться ні перед чим заради золота</t>
+          <t>Він неоднозначний</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Моряк якого пірати кинули на острові — він знайшов скарб раніше і став несподіваним союзником</t>
+          <t>Моряк якого пірати кинули на острові</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Більшість піратів гине або залишається на острові — золото дістається чесній команді</t>
+          <t>Більшість піратів гине або залишається на острові</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Хто такі сквайр Трелоні і доктор Лівсі у романі?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пірати</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Поважні люди, які організували експедицію за скарбом, дізнавшись про карту</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Моряки-найманці</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Родичі Джима</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Кого сквайр Трелоні найняв коком на корабель, не знаючи його минулого?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Капітана Смоллетта</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Довгого Джона Сілвера, колишнього пірата</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бена Ганна</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Біллі Бонса</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Як капітан Смоллетт почувався щодо екіпажу, найнятого Сілвером, ще до відплиття?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Повністю довіряв</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Підозрював, що команда підібрана не випадково, і був насторожений</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не звертав уваги</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сам найняв їх</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Як Джим випадково дізнався про план піратського бунту?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йому розповів Сілвер сам</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Заліз у бочку з яблуками за фруктом і почув розмову Сілвера з іншими піратами</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Прочитав записку</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Побачив зброю</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що Джим почув із розмови піратів у бочці?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Про шторм</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Про план захопити корабель і вбити чесну команду після знаходження скарбу</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Про маршрут додому</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Про їжу</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Що Джим зробив одразу після того, як почув цю розмову?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого, промовчав</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Таємно повідомив капітана Смоллетта, доктора Лівсі та сквайра про змову</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сказав Сілверу, що чув усе</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Утік з корабля</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Куди чесна частина команди перебралась, коли пірати взяли гору на кораблі?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишились на кораблі</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>До старого дерев'яного форту (частоколу) на острові</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У печеру</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На інший корабель</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що Джим зробив самостійно, попри заборону, поки інші захищали форт?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишився у форті</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тайкома відплив на човні, щоб перерізати якірний канат «Іспаньйоли»</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Здався піратам</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заснув на березі</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що сталося з човном Джима після того, як він перерізав канат корабля?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Човен прибило назад до форту</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Човен перекинувся, і Джим ледве дістався берега вплав</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Човен затонув з Джимом</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Човен здобули пірати</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Кого Джим зустрів на борту «Іспаньйоли», коли врешті піднявся на палубу?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Капітана Смоллетта</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пірата Ізраеля Гендса, єдиного, хто залишився на кораблі, та ще одного мертвого пірата</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сілвера</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бена Ганна</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що сталося в боротьбі між Джимом і Ізраелем Гендсом біля штурвала?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гендс одразу переміг</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Гендс кинув у Джима ножем, але Джим устиг вистрілити першим</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони домовились мирно</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Джим здався</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як Джим повернув контроль над кораблем після перемоги над Гендсом?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Покликав інших на допомогу</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Самостійно спрямував корабель і викинувся на берег, після чого повернувся до форту</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Залишив корабель у морі</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Спалив корабель</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що компанія шукачів знайшла на місці, позначеному на карті як скарб?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Скарб лежав там, де й мав бути</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Велику яму — скарбу там вже не було, що шокувало і піратів, і чесну команду</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Карту піратів</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зброю</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Хто насправді вже давно переніс увесь скарб у іншу печеру до прибуття експедиції?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сілвер</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бен Ганн, моряк, якого пірати колись кинули на острові</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Капітан Смоллетт</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто, скарб лишився на місці</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чому Бен Ганн допоміг чесній команді проти піратів?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йому наказали</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він давно мріяв повернутися додому і отримати свою частку, тож допоміг тим, хто був чесніший</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він боявся Сілвера</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не мав вибору</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Хто такі пікти у баладі «Вересовий трунок» Стівенсона?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сучасний народ Шотландії</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Стародавній малорослий народ Шотландії, переможений королем-завойовником</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вигадані істоти</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Плем'я з Африки</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Який секрет берегли пікти навіть під загрозою смерті?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Секрет золота</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Таємницю приготування «вересового меду» (трунку) з вересу</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Секрет зброї</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Місце скарбу</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чому новий король вимагав від останніх піктів видати секрет трунку?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йому потрібні були гроші</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Йому подобався смак напою, і він хотів володіти таємницею назавжди</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Йому наказали боги</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він хотів продати рецепт</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Хто з піктів залишився живим перед королем — і в якому складі?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сам король</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Старий батько і його юний син — останні двоє з усього народу</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Двоє братів</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Жінка з дитиною</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що запропонував зробити батько-пікт, перш ніж видати секрет трунку?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Видати секрет одразу</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Попросив короля спершу скинути його сина зі скелі в море, щоб той не здригнувся під час розмови</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Втекти разом</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Битися з королем</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Що насправді зробив батько, коли його сина скинули зі скелі?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Видав секрет, як і обіцяв</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сказав, що тепер, коли син мертвий, ніхто не змусить його зрадити таємницю, і помер з нею</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Утік</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Розплакався і нічого не сказав</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Вересового трунку»?</t>
+          <t>Головна ідея «Вересового трунку» — гідність і вірність своєму народові можуть бути сильнішими за страх смерті.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між «Островом скарбів» і «Вересовим трунком»?</t>
+          <t>І «Острів скарбів», і «Вересовий трунок» порушують теми відваги, честі та випробувань перед загрозою смерті.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>До якої теми належить образ останнього пікта у баладі?</t>
+          <t>Образ останнього пікта у баладі символізує остаточну й безславну капітуляцію цілого народу.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Що таке «Вересовий трунок» і який жанр цього твору Стівенсона?</t>
+          <t>«Вересовий трунок» — це балада Стівенсона про останніх піктів Шотландії та таємницю напою з вересу.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яку таємницю зберігали пікти у «Вересовому трунку»?</t>
+          <t>Пікти зберігали таємницю приготування напою з вересу навіть під загрозою смерті.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Чому батько у баладі просить стратити спочатку сина а потім себе?</t>
+          <t>Батько погодився видати секрет трунку зрештою, попри смерть сина.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси характеру виявляє Джим Хокінс в «Острові скарбів»?</t>
+          <t>Що сталося в романі «Острів скарбів»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Сміливість і кмітливість</t>
+          <t>Джим почув план бунту з бочки</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Вірність друзям</t>
+          <t>Джим переміг Ізраеля Гендса</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Жадібність до золота</t>
+          <t>Скарб лишився на місці незмінним</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Рішучість у небезпеці</t>
+          <t>Бен Ганн уже переніс скарб</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Справжні скарби — це відвага честь і вірність; жага золота руйнує людей</t>
+          <t>Справжні скарби</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Амбівалентність людської природи — він одночасно приваблює і відштовхує що робить його живим а не схематичним злодієм</t>
+          <t>Амбівалентність людської природи</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Активного героя чия сміливість і кмітливість часто рятують дорослих — підліток виявляється не менш здатним</t>
+          <t>Активного героя чия сміливість і кмітливість часто рятують дорослих</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
